--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$L$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,19 +37,23 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="16"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,12 +67,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,9 +113,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -604,7 +613,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -614,7 +623,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -624,7 +633,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -634,7 +643,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -655,7 +664,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>4.4</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -676,7 +685,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>3.684889641</v>
+        <v>0.454962062</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +695,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>-0.7151103590000005</v>
+        <v>-0.1450379380000001</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -800,51 +809,51 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Harry Potter flying car</t>
+          <t>wrappedape</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>wApe</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>WON</t>
+          <t>LOST</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="F2" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>0.193720911</v>
+        <v>0.166269841</v>
       </c>
       <c r="H2" s="12" t="n">
-        <v>-0.006279089000000015</v>
+        <v>-0.03373015900000001</v>
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 0.1% after 30s</t>
+          <t>trade-event stop-loss -14.1%</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>2VyRRmA2popb39MpxnXoBa4v7tj4YteJ5Yeu42rppump</t>
+          <t>CqZVFMMVxnz9VGENSXQLsRkJERsXWgR9iEy4gySypump</t>
         </is>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:33:45</t>
+          <t>2026-10-15 08:53:11</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:34:15</t>
+          <t>2026-10-15 08:53:11</t>
         </is>
       </c>
     </row>
@@ -854,51 +863,51 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Chinese RAM</t>
+          <t>PUMP</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>内存</t>
+          <t>PUMP</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>WON</t>
+          <t>LOST</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="F3" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.204906978</v>
+        <v>0.161794524</v>
       </c>
       <c r="H3" s="12" t="n">
-        <v>0.004906977999999979</v>
+        <v>-0.03820547600000002</v>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 5.9% after 30s</t>
+          <t>trade-event breakeven -16.3%</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>2U1gW43ea8QXqEQQcAPgZpdjPSjbTbS3Jh13k9hVpump</t>
+          <t>D58L4u1URrf1tMi6dRpG6rsnx1aDRDGNYqJiUPjhpump</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:33:46</t>
+          <t>2026-10-15 08:53:12</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:34:16</t>
+          <t>2026-10-15 08:53:13</t>
         </is>
       </c>
     </row>
@@ -908,51 +917,51 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>toshiba</t>
+          <t>Marlboro</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>TOSHIBA</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
+          <t>Headrush</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>LOST</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>-8.4%</t>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="F4" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.177354946</v>
+        <v>0.126897697</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>-0.022645054</v>
+        <v>-0.07310230300000001</v>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>watchdog stop-loss -8.4%</t>
+          <t>watchdog stop-loss -34.4%</t>
         </is>
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>CxA5edLYZePQYJSZjPpL8LE9RrrBy6sV6JGpkkMHpump</t>
+          <t>A12KPqnVfVPH8pZCaBFDqYZdDNhqr5Qp3vcWkBiUpump</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:33:47</t>
+          <t>2026-10-15 08:53:15</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:33:52</t>
+          <t>2026-10-15 08:53:17</t>
         </is>
       </c>
     </row>
@@ -962,53 +971,41 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Dolly</t>
+          <t>The Ozymandian Eagle</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Dolly</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>+2.9%</t>
-        </is>
-      </c>
+          <t>EAGLECOIN</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr"/>
       <c r="F5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="12" t="n">
-        <v>0.967182157</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>-0.03281784300000001</v>
-      </c>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr"/>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 2.9% (-16.5% from peak)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>FnyJBUbRq2q8sKLzgtgHj7tDquDEPK3HbR1KdVKzpump</t>
+          <t>55teXSXvAudgGEcPbAiw7CpExtMYbdtjFQNxwkSEpump</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:33:53</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:33:58</t>
-        </is>
-      </c>
+          <t>2026-10-15 08:53:21</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1016,53 +1013,41 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Last One Standing</t>
+          <t>streamoors</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>LASTONE</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>+5.6%</t>
-        </is>
-      </c>
+          <t>STREAM</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>0.204304496</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.004304495999999991</v>
-      </c>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 5.6% after 30s</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>2bv7Hu2X7upuQwtSFjycegjaUJCx4dgxyixyFL9cX64f</t>
+          <t>FdsdBhh9RwZ4Wn3JBfjdppuU2PxMwaM7xYygdKxypump</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:34:17</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:47</t>
-        </is>
-      </c>
+          <t>2026-10-15 08:53:23</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1070,272 +1055,44 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>LUMINOUS</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>LUMINOUS</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>-56.7%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0.413221214</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>-0.586778786</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>trade-event breakeven -56.7%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Ki95qhKwtZrsZuq9YbVHwG3j9KMudhf5tKQ3QjEpump</t>
+          <t>4SRt4msD7kMa95YURo5p4YBSGFhNyL1WmYzJtQjBmGwy</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:34:19</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Webster</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>+0.1%</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.193594342</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>-0.006405658000000009</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>watchdog dead-coin 0.1% after 30s</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>68CBaJ9N5W8GtrxqxvgmoGgG9qALr5aV2RnT3tX7pump</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:20</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>NYC Horse Carriage Ban</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>WAN</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>+6.6%</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.206203184</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.006203184</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>watchdog dead-coin 6.6% after 30s</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>92WK6q3QA3PRBMZDYkix2DYv5WFV8QJ7ohcJtGqbpump</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:51</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:35:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Forced Runner</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Runner</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>-6.4%</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0.181141959</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>-0.01885804100000002</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>trade-event breakeven -6.4%</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>FjUPh36x3raqf1CKJ9NTgQ3sHe5HmgBVFQnjMdeGpump</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:56</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>MAYA BLOOM</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>MAYA</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>+1.4%</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0.943259454</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>-0.056740546</v>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>watchdog dead-coin 1.4% after 30s</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>HEhjFpMB389SMmPw3qaSW1rF9dStUQuczDvoaLp7pump</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:34:57</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 07:35:27</t>
-        </is>
-      </c>
+          <t>2026-10-15 08:53:24</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$L$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,20 +37,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="6">
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,15 +107,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -132,6 +132,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -613,7 +616,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +626,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +636,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +646,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -653,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -664,7 +667,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -675,7 +678,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +688,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.454962062</v>
+        <v>0.449699276</v>
       </c>
     </row>
     <row r="19">
@@ -695,7 +698,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>-0.1450379380000001</v>
+        <v>0.04969927600000001</v>
       </c>
     </row>
     <row r="20">
@@ -724,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -809,53 +812,41 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>wrappedape</t>
+          <t>REAL CA IS ON TWEET READDD</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>wApe</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>-14.1%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G2" s="12" t="n">
-        <v>0.166269841</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>-0.03373015900000001</v>
-      </c>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>trade-event stop-loss -14.1%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>CqZVFMMVxnz9VGENSXQLsRkJERsXWgR9iEy4gySypump</t>
+          <t>9jzimoanzEHKupPtj4EAVXmucwSjCQVr98TCGLAupump</t>
         </is>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:53:11</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 08:53:11</t>
-        </is>
-      </c>
+          <t>2026-10-15 08:58:53</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -863,51 +854,51 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>Nihilism</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>PUMP</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+          <t>Nihilism</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>LOST</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>-16.3%</t>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="F3" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.161794524</v>
+        <v>0.181909038</v>
       </c>
       <c r="H3" s="12" t="n">
-        <v>-0.03820547600000002</v>
+        <v>-0.01809096200000002</v>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>trade-event breakeven -16.3%</t>
+          <t>watchdog stop-loss -6.3%</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>D58L4u1URrf1tMi6dRpG6rsnx1aDRDGNYqJiUPjhpump</t>
+          <t>sW4r5TkA1vSMR6bjge82rXR1KNNsSJnvRWTikkbc8mS</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:53:12</t>
+          <t>2026-10-15 08:58:54</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:53:13</t>
+          <t>2026-10-15 08:58:56</t>
         </is>
       </c>
     </row>
@@ -917,53 +908,41 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Marlboro</t>
+          <t>Dog Park</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Headrush</t>
+          <t>DOGPARK</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>-34.4%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr"/>
       <c r="F4" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>0.126897697</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>-0.07310230300000001</v>
-      </c>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>watchdog stop-loss -34.4%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>A12KPqnVfVPH8pZCaBFDqYZdDNhqr5Qp3vcWkBiUpump</t>
+          <t>BSFUrhXSc7tEkQ9aSaKFwTM8zBrwZEVdZV3jQGEETELE</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:53:15</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 08:53:17</t>
-        </is>
-      </c>
+          <t>2026-10-15 08:58:56</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -971,128 +950,56 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>The Ozymandian Eagle</t>
+          <t>CATECOIN</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>EAGLECOIN</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr"/>
+          <t>$CAT</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>+39.1%</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.267790238</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.067790238</v>
+      </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog trailing-stop 39.1% (-48.3% from peak)</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>55teXSXvAudgGEcPbAiw7CpExtMYbdtjFQNxwkSEpump</t>
+          <t>dxpPKBxotMDK3vXDAczw9SUSYkPdqrAujB9SAMkpump</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:53:21</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>streamoors</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>STREAM</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>FdsdBhh9RwZ4Wn3JBfjdppuU2PxMwaM7xYygdKxypump</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 08:53:23</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>4SRt4msD7kMa95YURo5p4YBSGFhNyL1WmYzJtQjBmGwy</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 08:53:24</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr"/>
+          <t>2026-10-15 08:58:57</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:58:58</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1117,42 +1024,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$L$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -115,7 +115,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.449699276</v>
+        <v>0.650663157</v>
       </c>
     </row>
     <row r="19">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.04969927600000001</v>
+        <v>-0.349336843</v>
       </c>
     </row>
     <row r="20">
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -812,12 +812,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>REAL CA IS ON TWEET READDD</t>
+          <t>Biscuit</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>Biscuit</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>9jzimoanzEHKupPtj4EAVXmucwSjCQVr98TCGLAupump</t>
+          <t>4K2bzeQQmBPfJeSPh4MUBhf7MCX1iK35dh2Mjwrtpump</t>
         </is>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:58:53</t>
+          <t>2026-10-15 09:12:26</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Nihilism</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Nihilism</t>
+          <t>$BYD</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -869,36 +869,36 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="F3" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.181909038</v>
+        <v>0.093941554</v>
       </c>
       <c r="H3" s="12" t="n">
-        <v>-0.01809096200000002</v>
+        <v>-0.106058446</v>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>watchdog stop-loss -6.3%</t>
+          <t>trade-event stop-loss -51.4%</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>sW4r5TkA1vSMR6bjge82rXR1KNNsSJnvRWTikkbc8mS</t>
+          <t>3zcRy61grA6KCrxKLnHz3kFsj6DghRxCwa1Zhjmrpump</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:58:54</t>
+          <t>2026-10-15 09:12:29</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:58:56</t>
+          <t>2026-10-15 09:12:29</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Dog Park</t>
+          <t>Discord Mod</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>DOGPARK</t>
+          <t>DiscMod</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>BSFUrhXSc7tEkQ9aSaKFwTM8zBrwZEVdZV3jQGEETELE</t>
+          <t>9dnTGSKS1q1hv2stduthT5Ph2JVC9Jsh8Fj2bgeTpump</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:58:56</t>
+          <t>2026-10-15 09:12:30</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr"/>
@@ -950,56 +950,218 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>CATECOIN</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>$CAT</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>+39.1%</t>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.267790238</v>
+        <v>0.183843211</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>0.067790238</v>
+        <v>-0.016156789</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 39.1% (-48.3% from peak)</t>
+          <t>trade-event breakeven -4.9%</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>dxpPKBxotMDK3vXDAczw9SUSYkPdqrAujB9SAMkpump</t>
+          <t>8AmrN25dYemThizkG6qjcdthvgYrnZcHvBPVZKqSpump</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:58:57</t>
+          <t>2026-10-15 09:12:32</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 08:58:58</t>
+          <t>2026-10-15 09:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>BOTCOIN</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>$BOT</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>-69.6%</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.058812368</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>-0.141187632</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -69.6%</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>4DuqSQqow3uHEDukrXh53FTckMWHifPR6NCShNigpump</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:12:41</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:12:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0.111060535</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>-0.08893946500000001</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 6.2% (-48.3% from peak)</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>3siM9nfVBRCvN2WS2rthbvX9Dm68jMchkxthvT4Wpump</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:12:45</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Doomed Rocket</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>DOOROC</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>+4.9%</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.203005489</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.003005489</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 4.9% (-24.4% from peak)</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>HwiEQtx6xfNZvp73j6AmDQ8mYGvSaS2q2jeR3Huipump</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:12:47</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:12:48</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +45,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +113,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -667,47 +667,71 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Total invested (SOL)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>1</v>
+          <t>Avg peak (MFE)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>+41.4%</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Total back (SOL)</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>0.650663157</v>
+          <t>Avg drawdown (MAE)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>-17.0%</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (SOL)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>-0.349336843</v>
+          <t>Total invested (SOL)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Total back (SOL)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1.053916809</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (SOL)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>-0.1460831910000002</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Excel file</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>D:\AI\solana-trading-bot\reports\pumpfun_trades.xlsx</t>
         </is>
@@ -727,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -735,13 +759,15 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -772,35 +798,45 @@
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
+          <t>MFE %</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>MAE %</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
           <t>Invested SOL</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Exit SOL</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Profit/Loss SOL</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Bought at</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Sold at</t>
         </is>
@@ -812,41 +848,63 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Biscuit</t>
+          <t>Nihl</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Biscuit</t>
+          <t>NIHL</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="12" t="n">
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>+6.7%</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>4K2bzeQQmBPfJeSPh4MUBhf7MCX1iK35dh2Mjwrtpump</t>
-        </is>
+      <c r="I2" s="12" t="n">
+        <v>0.199762023</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>-0.0002379770000000003</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:26</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr"/>
+          <t>watchdog dead-coin 3.3% after 30s</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>2EgByTVv7GQqCGSiQhEtQ4io2h4UmPSkZYbr2pTUpump</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:22</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:52</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -854,12 +912,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>UNUS SED LEO</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>$BYD</t>
+          <t>LÉO</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -869,36 +927,46 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>-51.4%</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n">
+          <t>-50.7%</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>-50.7%</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G3" s="12" t="n">
-        <v>0.093941554</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>-0.106058446</v>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>trade-event stop-loss -51.4%</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>3zcRy61grA6KCrxKLnHz3kFsj6DghRxCwa1Zhjmrpump</t>
-        </is>
+      <c r="I3" s="12" t="n">
+        <v>0.09529591499999999</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>-0.104704085</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:29</t>
+          <t>trade-event stop-loss -50.7%</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:29</t>
+          <t>6DYL4Eb3u49rDYDBiP7Pt4nCUQ7k4E15wjBkhmd8pump</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:25</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:25</t>
         </is>
       </c>
     </row>
@@ -908,41 +976,43 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Discord Mod</t>
+          <t>PSI</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>DiscMod</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="12" t="n">
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr"/>
+      <c r="G4" s="9" t="inlineStr"/>
+      <c r="H4" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G4" s="10" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>holding</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>9dnTGSKS1q1hv2stduthT5Ph2JVC9Jsh8Fj2bgeTpump</t>
-        </is>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:12:30</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr"/>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>DAfUDBqZLtghKRjnGryHT5ic7mGmBo2b7feyvrhipump</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:27</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -950,12 +1020,12 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Chaotic Rocket</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>CHAROC</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -965,36 +1035,46 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>-4.9%</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n">
+          <t>-51.3%</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>-51.3%</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G5" s="12" t="n">
-        <v>0.183843211</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>-0.016156789</v>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>trade-event breakeven -4.9%</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>8AmrN25dYemThizkG6qjcdthvgYrnZcHvBPVZKqSpump</t>
-        </is>
+      <c r="I5" s="12" t="n">
+        <v>0.09412549200000001</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>-0.105874508</v>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:32</t>
+          <t>watchdog stop-loss -51.3%</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:39</t>
+          <t>HrvV3ubuY2rWgdYPc1tfTgE6MzwVop6uTN4vLtV1pump</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:29</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:31</t>
         </is>
       </c>
     </row>
@@ -1004,51 +1084,61 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>BOTCOIN</t>
+          <t>TRUMPISM</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>$BOT</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>-69.6%</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
+          <t>$TRMPSM</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>+132.0%</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>0.058812368</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>-0.141187632</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>trade-event stop-loss -69.6%</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>4DuqSQqow3uHEDukrXh53FTckMWHifPR6NCShNigpump</t>
-        </is>
+      <c r="I6" s="12" t="n">
+        <v>0.194717265</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>-0.005282735000000011</v>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:41</t>
+          <t>watchdog trailing-stop 0.6% (-56.6% from peak)</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:41</t>
+          <t>C4zPh1LoacouSFyusuJDVAukKKGmPJnGW9j35F9ypump</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:33</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:35</t>
         </is>
       </c>
     </row>
@@ -1058,51 +1148,61 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Super General Robot</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>+6.2%</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>+39.1%</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+75.8%</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>0.111060535</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>-0.08893946500000001</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 6.2% (-48.3% from peak)</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>3siM9nfVBRCvN2WS2rthbvX9Dm68jMchkxthvT4Wpump</t>
-        </is>
+      <c r="I7" s="12" t="n">
+        <v>0.268779474</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.06877947400000001</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:45</t>
+          <t>watchdog trailing-stop 39.1% (-20.9% from peak)</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:45</t>
+          <t>6zLWahuStCZCVjgFc1gwPZ6dE9vkjoswWysKrHQ9pump</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:40</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:41</t>
         </is>
       </c>
     </row>
@@ -1112,56 +1212,154 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Doomed Rocket</t>
+          <t>@k</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>DOOROC</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
+          <t>@K</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>+4.9%</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>+33.1%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G8" s="12" t="n">
-        <v>0.203005489</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.003005489</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 4.9% (-24.4% from peak)</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>HwiEQtx6xfNZvp73j6AmDQ8mYGvSaS2q2jeR3Huipump</t>
-        </is>
+      <c r="I8" s="12" t="n">
+        <v>0.20123664</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>0.001236639999999983</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:47</t>
+          <t>watchdog trailing-stop 4.0% (-21.9% from peak)</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:12:48</t>
-        </is>
-      </c>
+          <t>8NVp9cQZug3a8gLjqBsqrffwtgqjy6HJVdScxRPBpump</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:44</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Bonsai</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Bonsai</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>26uP3eBS2zCvNGduhou2uTPQvydtrdFKxaVBznpmpump</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:53</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>The Bitcoin Cat</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>TheCat</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>6xMShQxQpPcXxBUUX7hxvGiYJHsohgEYJz6woNvVpump</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:17:54</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,15 +45,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +69,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,9 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,9 +123,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -616,7 +604,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -626,7 +614,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +624,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -646,7 +634,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +644,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +655,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -679,7 +667,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+41.4%</t>
+          <t>+5.7%</t>
         </is>
       </c>
     </row>
@@ -691,7 +679,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
     </row>
@@ -702,7 +690,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -712,7 +700,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1.053916809</v>
+        <v>0.7419586140000001</v>
       </c>
     </row>
     <row r="21">
@@ -722,7 +710,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>-0.1460831910000002</v>
+        <v>-0.05804138599999997</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -848,12 +836,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Nihl</t>
+          <t>HE HAS A CONFIRMED WALLET???</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>NIHL</t>
+          <t>Nihilism</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -863,12 +851,12 @@
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -880,29 +868,29 @@
         <v>0.2</v>
       </c>
       <c r="I2" s="12" t="n">
-        <v>0.199762023</v>
+        <v>0.193466246</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>-0.0002379770000000003</v>
+        <v>-0.006533754000000003</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 3.3% after 30s</t>
+          <t>watchdog dead-coin 0.0% after 30s</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>2EgByTVv7GQqCGSiQhEtQ4io2h4UmPSkZYbr2pTUpump</t>
+          <t>HYFhhCTgzKNwjDWgNXQGPiNXyRgTojhYhDPf3ZTbpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:17:22</t>
+          <t>2026-10-15 09:32:42</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:17:52</t>
+          <t>2026-10-15 09:33:12</t>
         </is>
       </c>
     </row>
@@ -912,22 +900,22 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>UNUS SED LEO</t>
+          <t>HE HAS A CONFIRMED WALLET???</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>LÉO</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>-50.7%</t>
+          <t>Nihilism</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -937,36 +925,36 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="H3" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>0.09529591499999999</v>
+        <v>0.193466246</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>-0.104704085</v>
+        <v>-0.006533754000000003</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>trade-event stop-loss -50.7%</t>
+          <t>watchdog dead-coin 0.0% after 30s</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>6DYL4Eb3u49rDYDBiP7Pt4nCUQ7k4E15wjBkhmd8pump</t>
+          <t>7VYnAe6TBHijsr3rW2TxhVcTAjvVFFBXTnfZrXsEpump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:17:25</t>
+          <t>2026-10-15 09:32:43</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:17:25</t>
+          <t>2026-10-15 09:33:13</t>
         </is>
       </c>
     </row>
@@ -976,43 +964,63 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>PSI</t>
+          <t>HE HAS A CONFIRMED WALLET???</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>PSI</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
+          <t>Nihilism</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H4" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
+      <c r="I4" s="12" t="n">
+        <v>0.193466246</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>-0.006533754000000003</v>
+      </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog dead-coin 0.0% after 30s</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>DAfUDBqZLtghKRjnGryHT5ic7mGmBo2b7feyvrhipump</t>
+          <t>8tKTLE9JG2KkW1ry1tGbZNquRQFhK2RTAamKGiMVpump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:17:27</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr"/>
+          <t>2026-10-15 09:32:45</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -1020,12 +1028,12 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Chaotic Rocket</t>
+          <t>fork it to ya</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>CHAROC</t>
+          <t>forkya</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -1035,331 +1043,51 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+21.6%</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="H5" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>0.09412549200000001</v>
+        <v>0.161559876</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>-0.105874508</v>
+        <v>-0.03844012400000002</v>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>watchdog stop-loss -51.3%</t>
+          <t>watchdog breakeven -16.5%</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>HrvV3ubuY2rWgdYPc1tfTgE6MzwVop6uTN4vLtV1pump</t>
+          <t>4MTRYyKdXDP5FJKWARKMBYPKLPHzRbNC9vgLp7Lppump</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:17:29</t>
+          <t>2026-10-15 09:33:15</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:17:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>TRUMPISM</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>$TRMPSM</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>+0.6%</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>+132.0%</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I6" s="12" t="n">
-        <v>0.194717265</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>-0.005282735000000011</v>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 0.6% (-56.6% from peak)</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>C4zPh1LoacouSFyusuJDVAukKKGmPJnGW9j35F9ypump</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:33</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Super General Robot</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>+39.1%</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>+75.8%</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>0.268779474</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>0.06877947400000001</v>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 39.1% (-20.9% from peak)</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>6zLWahuStCZCVjgFc1gwPZ6dE9vkjoswWysKrHQ9pump</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:40</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>@k</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>@K</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>+4.0%</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>+33.1%</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>0.20123664</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>0.001236639999999983</v>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 4.0% (-21.9% from peak)</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>8NVp9cQZug3a8gLjqBsqrffwtgqjy6HJVdScxRPBpump</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:44</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Bonsai</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Bonsai</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>26uP3eBS2zCvNGduhou2uTPQvydtrdFKxaVBznpmpump</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:53</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>The Bitcoin Cat</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>TheCat</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>6xMShQxQpPcXxBUUX7hxvGiYJHsohgEYJz6woNvVpump</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:17:54</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr"/>
+          <t>2026-10-15 09:33:16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1384,42 +1112,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,11 +45,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,9 +107,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,7 +134,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -604,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -614,7 +629,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -624,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -634,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -644,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -655,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -667,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+5.7%</t>
+          <t>+32.7%</t>
         </is>
       </c>
     </row>
@@ -679,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-10.8%</t>
         </is>
       </c>
     </row>
@@ -690,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="20">
@@ -700,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>0.7419586140000001</v>
+        <v>18.512674942</v>
       </c>
     </row>
     <row r="21">
@@ -710,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>-0.05804138599999997</v>
+        <v>-3.087325058000001</v>
       </c>
     </row>
     <row r="22">
@@ -739,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1086,8 +1101,5260 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>-57.9%</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>+294.7%</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>-57.9%</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>0.402469665</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>-0.5975303350000001</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>trade-event breakeven -57.9%</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>3C4z3rCKL7cXkYpyVXGLnACkr3tKqbEJpibha9MApump</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:28</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Blinko</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Blinko</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>+11.4%</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+49.6%</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>0.215441969</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.015441969</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 11.4% (-25.6% from peak)</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>8qYHudsPhgGX3cxQKt5h4PxQugyJBxbaEH11s14Cpump</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:30</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>STONKASAURUS</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>$DINO</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>-23.2%</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>-23.2%</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>0.148507063</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>-0.05149293700000002</v>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -23.2%</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>2ertg8k39qDr4Gg9sFFeAUMJdJTXVUUJtvsbWjPEpump</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:31</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>falling guy</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>fg</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>-70.5%</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>-70.5%</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.056993072</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>-0.143006928</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -70.5%</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>HiEDbbzeuQnxwa4w9NNCa2E6wEBm54roqrjXYz1gpump</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:33</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Holy Fries</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Fries</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>+18.6%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>0.188126204</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>-0.01187379600000002</v>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>trade-event breakeven -2.8%</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>EHoh2Ph2Pakd5hvGjZLra1ePyEQ4KJy1gfcNDUSMpump</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:36</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>SpaceXTeslaXAI</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>SEXSI</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>+89.2%</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>+138.2%</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>0.365141844</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.165141844</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 89.2% (-20.6% from peak)</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>AQJajNndyvDetjsPP624LuVy65yDcnjVJNU35275e5Mx</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:37</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>SpaceXTeslaXAI</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>SEXSI</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0.101736459</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>-0.09826354100000001</v>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>watchdog breakeven 0.0%</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>CWUaqthjR93D7926VgbnYKpCPpgbEKfVjzdfmSxNVmnt</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:39</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>TeslaX</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>TSLAX</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>+49.2%</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>+86.7%</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>0.28824842</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.08824841999999999</v>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 49.2% (-20.1% from peak)</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>6dzQkSE32YUYUByunfbXPM3XJY1yFaco5qc3JcQ2pump</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:49</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>TeslaX</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>TSLAX</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>0.101736459</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>-0.09826354100000001</v>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>7W549QDmXv2jmQCQwgZoNJp4Erionm1XxXfRPe5m5ur2</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:51</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Unsaid</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>UNSAID</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>-100.0%</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>+19.2%</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>-100.0%</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>trade-event emergency-flat -100.0%</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>3KyZVAesnwcLpy7gwiyYZxKYkjBkN9ojCQXGHy5ppump</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:52</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>SpaceXTeslaXSI</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>SEXSI</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>-3.7%</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>+20.4%</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>-3.7%</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0.906764716</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>-0.09323528400000003</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>watchdog breakeven -3.7%</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>AzTkrM9EhA4W2N1rEZJWGhpFs3WtHedVD3hjEsSjpump</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:53</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>PNUT + BONK</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>PONK</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>0.199881752</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>-0.0001182480000000152</v>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 3.3% after 30s</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>4GPMU2xgxhCrDs11GCb8kFV53rUrFKGfPzgLhWmZpump</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:59</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>memristor</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>memristor</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>+8.1%</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>+79.6%</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>1.011253705</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>0.01125370499999989</v>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 8.1% (-18.6% from peak)</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>6dofwKPaHCMfiZiYLTuiFcBvGrjK6CXL9RRQButhpump</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:01</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>ditto</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>ditto</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>+36.1%</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>0.193466246</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>-0.006533754000000003</v>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 0.0% (-26.5% from peak)</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>Deqzze2Vrb6BERxBcM585JgHwtPmBfZAkhbBXzmBGiSk</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:23</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>+57.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>+285.8%</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>1.486677282</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0.486677282</v>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 57.5% (-15.1% from peak)</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>2MCSv6nLDEVvdrd2hAJLDqwjDxcM6qYjgkNUBUfqpump</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:24</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POW </t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POW </t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>-19.5%</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>-19.5%</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>0.155845687</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>-0.044154313</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -19.5%</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>2TVUatbaYGUasGpHv14ndPwcvh3qKU3eJNR3u94mpump</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:35</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>dirk jetah</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>dirkjetah</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>-75.4%</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>-75.4%</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>0.047551967</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>-0.152448033</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -75.4%</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>AdXnkrKr4c5sbSqzb51UVRZHKBTy38k9WkYvuMrQpump</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:36</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>gayhorse</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>gayhorse</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0.193467943</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>-0.006532057000000008</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>Cuoq76UfD9rFx6V6p3udyQmSEYcoNQPoRYFFm8TFpump</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:38</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>i nuke u</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>inu</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>-12.8%</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>-12.8%</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0.169356165</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>-0.03064383500000001</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -12.8%</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>ArqDJLcoM7p57VFni8HKXwKA7ZFwyCosnBJxX9wtpump</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:39</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Doomed Rocket</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>DOOROC</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>0.192223502</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>-0.007776498000000021</v>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin -0.6% after 30s</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>2foGQepDcu1pV4qYHNYqKPU8cFcV7bAkg5pMkf6xpump</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:40</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>SpaceXTeslaXSI</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>SEXSI</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>0.182239743</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>-0.017760257</v>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -5.9%</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>8ov4hYNkfirkMGi4EC2Bhh3rqwGES7M8vAcaUfBypump</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:42</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>TRUMPY</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>🎺</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>-37.4%</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>-37.4%</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>0.121194531</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>-0.07880546900000002</v>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -37.4%</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>38aiztfpy37A2mttCrikoyPKBg2Ybfg6Eq2SoH4apump</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:49</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Wallet Racers</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>WALLET RACERS</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>+6.7%</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>+12.9%</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>0.206370194</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>0.006370193999999996</v>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>trade-event dead-coin 6.7% after 30s</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>9FuWxvuHAx7UKu1ERqcyDnF6WP5iFmmuoHiJdncmpump</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:53</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Tesla SpaceX</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>TESLAX</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>+3.5%</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>+3.5%</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>0.200139307</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>0.0001393069999999774</v>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 3.5% after 30s</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>FA2KMrg7Pu6GiFDoVAtJd4eN664VMfAWBqsqyz1cpump</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:11</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Robinhood Agents</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>-43.7%</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>-43.7%</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0.108962218</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>-0.09103778200000001</v>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -43.7%</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>4FhgqQ5kCx38XMyo1v2XM2edsEgSyrgRh1x2VKqapump</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:16</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Critters</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>CRITTERS</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>+9.6%</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>+30.9%</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>0.211981268</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>0.01198126799999999</v>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 9.6% (-16.3% from peak)</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>6tv63HegjDJSZaRNkp25BarvkQaFAwFzCX1zYF7bpump</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:20</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:36:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Daimonia AI</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Daimonia</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>+9.3%</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>+23.1%</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>0.211324067</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>0.01132406699999999</v>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>trade-event dead-coin 9.3% after 30s</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>3EiNwACMH517bBapRgK4VrvcQHCmePbNzWAMwZHBpump</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:35:46</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Grouch</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Grouch</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>-13.9%</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>+1.3%</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>-13.9%</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>0.166599779</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>-0.03340022100000001</v>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -13.9%</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>7aegjJeYcXRtxzLBgAX7Wpk72Qndy7K9jYF46NAMpump</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:36:21</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POW </t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POW </t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>+2.0%</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>+33.4%</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0.197303332</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>-0.002696668000000013</v>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 2.0% (-23.5% from peak)</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>3r8SckjqnPYY4cSZK5gxAYueRiwDyU7AA8z1dMjXpump</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:36:27</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:36:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Miko Protocol</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>MIKO</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>+6.7%</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>+24.1%</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>0.206370195</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>0.006370194999999995</v>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>trade-event dead-coin 6.7% after 30s</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>Ds48aLHDaX4v2qZQ9UEwcxFuhhN1bHwADE55n5ZPpump</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:36:34</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>FUCK ALL YALL FAGGOTS</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>SLOW NIGS</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>0.101736459</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>-0.09826354100000001</v>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>watchdog breakeven 0.0%</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>5fFXV9k1DgWUvpd8qFx1YyyohoCE27GT1rvfLXh2pump</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:09</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>FUCK ALL YALL FAGGOTS</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>SLOW NIGS</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>0.101736459</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>-0.09826354100000001</v>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>watchdog breakeven 0.0%</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>DvMYzpMgvgCb4sTCS1tJjH7U2Nc4KcEUrNqkkv8epump</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:11</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Sevda</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Sevda</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>+35.8%</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>0.19980093</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>-0.0001990700000000234</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 3.3% (-24.0% from peak)</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>H5fJBmUYuFUT9HLEd1GB7eEEWzbfwAihPUVYRAtMpump</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:20</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>rghj</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>RGHJ</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>0.01031363</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>-0.18968637</v>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 0.0% (-99.0% from peak)</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Cqq3ZTppP7VHuiEwRS6mfvaiTHQax9JeE1KEDLcqizjt</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:28</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Existentialism</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>+15.0%</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>0.212109166</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>0.01210916599999998</v>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>trade-event dead-coin 9.7% after 30s</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>47S4nzYbdQBfabVJjbkGyyjn1gSXLfLBzuNoB4SBpump</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:29</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clapping Cat </t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Ccat</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>+6.7%</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>+8.0%</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>0.206399007</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>0.006399006999999984</v>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 6.7% after 30s</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Akg6REXrHPPYYYZfx9kYooSnDKGtTiAtHatw3Zsdpump</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:30</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>oldgame</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>oldgame</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>+77.3%</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>0.194741201</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>-0.005258799000000008</v>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 0.7% (-43.2% from peak)</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>AXCAKpMEBitKzpYHotufPrTa1H7QADLN73UkLXfYpump</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:03</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Robinhood Agents</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>+31.2%</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>0.194221165</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>-0.00577883500000001</v>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 0.4% (-23.5% from peak)</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>7n5SvcAb2zDjDuXvgnDEJoDfgfA5BE4ygBqtciYppump</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:09</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>HYPE AI QUANTUM</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>HAIQ</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>-26.3%</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>-26.3%</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>0.142566542</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>-0.05743345800000002</v>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -26.3%</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>HvzhqfYiKzmG8mN9nZ2hAZ2RuKnDGhtkXHicAzpQpump</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:11</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>JEETS OUT CHADS IN</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>JOCI</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>0.101736459</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>-0.09826354100000001</v>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>9X3jVWTAZRkGhxdTGStAVfBABn9rXAdrxvUJtNuPpump</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:13</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Larplism</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Larplism</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>+9.8%</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>+11.2%</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>0.212358116</v>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>0.012358116</v>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 9.8% after 30s</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>BXn9YBzhiPaf5ooH6kYWbywDqURhTkhW7nMvdzCcpump</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:14</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>oldgame</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>oldgame</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>+1.3%</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>+35.0%</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>0.196020229</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>-0.003979771000000021</v>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 1.3% (-25.0% from peak)</t>
+        </is>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>9JW7hBCzhEmftXVZHSbAzLjrQZhMa9qn17gYQUoDpump</t>
+        </is>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:49</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:38:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>STENKS</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>STENKS</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>-13.2%</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>+21.1%</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>-13.2%</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>0.16790218</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>-0.03209782</v>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>trade-event breakeven -13.2%</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>DXGowm1fmndYBuvWcF1wDRyiG8kZLz2JxMmTsLSmpump</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:04</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>SOOTS</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>0.194221165</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>-0.00577883500000001</v>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.4% after 30s</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>CUtZ8ZERwqjj6kg2dnN6z23X44pqvuo2CtUdYnpppump</t>
+        </is>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:06</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nihilism </t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>nihilism</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>+8.6%</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>+25.5%</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>0.210003258</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>0.01000325799999999</v>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 8.6% after 30s</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>8ryinj89hAH2fRh8WCHrcoDhF4SaQxRE5KDgSxbopump</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:08</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Scream Cat</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Boo</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>0.194738018</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>-0.005261981999999998</v>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.7% after 30s</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>63iMtQ4GFum9jUTJ13jNiyLcFKn3xTKSvhkYQfCNpump</t>
+        </is>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:13</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>CALLOUT SCAN</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>-100.0%</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>+13.4%</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>-100.0%</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>trade-event emergency-flat -100.0%</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>GnK8R5DEeR3Lrd4zJBwg6wfT2cugunkJakYvcHASpump</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:45</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>nihili.sm</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>NIHILISM</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>0.194753941</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>-0.005246058999999997</v>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.7% after 30s</t>
+        </is>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>9PwUjiQhBfGzMuAk4XqSNiYU9gVpiTSvzQCXcpr5vW3d</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:54</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Nihilism Inu</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>+20.9%</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>+44.9%</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>0.233710898</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>0.03371089799999999</v>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 20.9% (-16.6% from peak)</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>Z8dgHNaf88CfZE8kJXBbp6F8tVyP16bjuHP3uBwpump</t>
+        </is>
+      </c>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:55</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Nihilism Inu</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>0.101736459</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>-0.09826354100000001</v>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>watchdog breakeven 0.0%</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="inlineStr">
+        <is>
+          <t>534QgDQqTuz6A2pMYatGrxVxKpfhcbRpVgQvVtHnNhVJ</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:56</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Justice for Benny</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Benny</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>+55.4%</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>+92.8%</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>0.300204517</v>
+      </c>
+      <c r="J56" s="12" t="n">
+        <v>0.100204517</v>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 55.4% (-19.4% from peak)</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>8Z168xB7BgaosbuEC8JXPuQyf62wEGPTjvtLKq13pump</t>
+        </is>
+      </c>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:39:58</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>My Sons Drawing of Safe</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>+9.5%</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>0.204687632</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>0.004687631999999997</v>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 5.8% after 30s</t>
+        </is>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>B7z8nxBTomW43wiUe164P6ARh86T2SYKguznobJ9pump</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:14</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>EGO</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>EGO</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>0.139093479</v>
+      </c>
+      <c r="J58" s="12" t="n">
+        <v>-0.06090652100000002</v>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 0.6% (-31.2% from peak)</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>DgK5wRNGNPCXzdE9i2119ZEKubncPRZzGNZrjzYjpump</t>
+        </is>
+      </c>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:15</t>
+        </is>
+      </c>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>On The Line</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>+2.6%</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>+31.3%</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>0.198394892</v>
+      </c>
+      <c r="J59" s="12" t="n">
+        <v>-0.001605108000000022</v>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 2.6% (-21.9% from peak)</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>RBj6DJ5MCtckae4HPVREcq9KUrBB8XtphB6cw3Upump</t>
+        </is>
+      </c>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:21</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>ULTRAPAID</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>ULTRA</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>-48.3%</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>-48.3%</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>0.100105787</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>-0.09989421300000001</v>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -48.3%</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>CfJBKKCQgRxaZQuh8NfWD3wNLouVRXYwtnVtPntapump</t>
+        </is>
+      </c>
+      <c r="M60" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:25</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Unsaid</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>UNSAID</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>+58.9%</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>+88.7%</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>0.306820361</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>0.106820361</v>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 58.9% (-15.8% from peak)</t>
+        </is>
+      </c>
+      <c r="L61" s="10" t="inlineStr">
+        <is>
+          <t>5WZZWT9CmTmu4VR7EiqcL6At727gtCSH1hoXCF8zpump</t>
+        </is>
+      </c>
+      <c r="M61" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:49</t>
+        </is>
+      </c>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>DOGE FORCE ONE</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>$DF1</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>-39.4%</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>+34.1%</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>-39.4%</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>0.11727896</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>-0.08272104000000001</v>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>trade-event breakeven -39.4%</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>5967AX67gnFrxiMcwXPdmF14z8EpL1oPRys1AFzQpump</t>
+        </is>
+      </c>
+      <c r="M62" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:50</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>BALK</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>BALK</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>-6.7%</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>-6.7%</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>0.180951761</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>-0.01904823900000002</v>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -6.7%</t>
+        </is>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>HukHKYAj8DNsDN9mmzkfx75HzJCVRuf8EN1EwuNpump</t>
+        </is>
+      </c>
+      <c r="M63" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:51</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Malfloyd</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>MFLOYD</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr"/>
+      <c r="F64" s="9" t="inlineStr"/>
+      <c r="G64" s="9" t="inlineStr"/>
+      <c r="H64" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I64" s="10" t="inlineStr"/>
+      <c r="J64" s="10" t="inlineStr"/>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>EMVC7v7RDdpJogoE6rqN7mDec63ZDn6qi3KrhJnmpump</t>
+        </is>
+      </c>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:53</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>SOOTS</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>-13.9%</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>-13.9%</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>0.166561874</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>-0.03343812600000001</v>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -13.9%</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="inlineStr">
+        <is>
+          <t>3Hdham371e5TLNgjzdMmYcMRYnrkd2sQQTNjPA1Ypump</t>
+        </is>
+      </c>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:55</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>MFOX</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>MEME FOX</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>0.207329394</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>0.007329393999999989</v>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 7.2% after 30s</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>Hx1j1hhhe9iMzgw7hUQgX1xVothVU8hFkHZ99qxEpump</t>
+        </is>
+      </c>
+      <c r="M66" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:56</t>
+        </is>
+      </c>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:41:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Mutate Pad</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Mutate</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>+29.2%</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>0.194863147</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>-0.005136853000000025</v>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.7% after 30s</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>GevSEKuW9tF1D8RjwJhvBjyWR5f8AX3jVbjpqHKkpump</t>
+        </is>
+      </c>
+      <c r="M67" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:40:57</t>
+        </is>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:41:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Netrun</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>NETRUN</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>0.193466246</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>-0.006533754000000003</v>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>2wxWqojmsZynh5ze2W5sDqF6mFnCUrVDASmwXSvRpump</t>
+        </is>
+      </c>
+      <c r="M68" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:41:28</t>
+        </is>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:41:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Squirtle</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>SQRTL</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>+4.3%</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>0.200976939</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>0.0009769389999999822</v>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 3.9% after 30s</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>714SUYnFj6gje5FrrQQZoz5YaKh2Hu8Zzv2cDDz4pump</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:41:30</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:42:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Larplism</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Larplism</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>+12.2%</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I70" s="12" t="n">
+        <v>0.199321763</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>-0.0006782369999999982</v>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 3.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>DpUebA8P36dXhWY32ai6kixQ3wca2rMXzZpZbSRvpump</t>
+        </is>
+      </c>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:42:00</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:42:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>-47.2%</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>+294.8%</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>-47.2%</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>0.504169065</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>-0.495830935</v>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>trade-event breakeven -47.2%</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>8YTmMy5xyY13tQ1CfTy31mWQACRoXqL53weAGxtQpump</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:42:02</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Grok Merch</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>GrokMerch</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>+20.4%</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>+42.6%</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>0.232871333</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>0.032871333</v>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 20.4% (-15.5% from peak)</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>3u14MkQSJBY54MMGyQhfL246YXAzsXsmMNZLQ73rpump</t>
+        </is>
+      </c>
+      <c r="M72" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:42:41</t>
+        </is>
+      </c>
+      <c r="N72" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:42:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Halloween Onboarding</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>WEENBOARD</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>+15.2%</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>+37.3%</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>0.22271341</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>0.02271340999999999</v>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 15.2% (-16.1% from peak)</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>8BBvM5BQtb6nhVhHyawqNsjJzM1jcSvNuKni1cb3pump</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:42:59</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:43:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Who Misses Owl</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>OWL</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>+3.6%</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>+23.9%</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>0.200312238</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>0.0003122379999999925</v>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>trade-event dead-coin 3.6% after 30s</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>DKhxKorhVAqNN2Sjks5g19GhwJUW8ZSufnvu3AYspump</t>
+        </is>
+      </c>
+      <c r="M74" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:43:15</t>
+        </is>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Dihlisim</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Dihlisim</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>+13.6%</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>0.193466246</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>-0.006533754000000003</v>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>trade-event dead-coin 0.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>6C22KBqjo12pdaZrS1NNq3NdTGJosb4twZ8GoU9Tpump</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:43:23</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Doomed Yeti</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>DOOYET</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>-13.8%</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>-13.8%</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>0.166842252</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>-0.03315774800000001</v>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -13.8%</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>8zHyGc7LPxLMJpEWnVBsH4JHxs5kLituQJvFgpnGpump</t>
+        </is>
+      </c>
+      <c r="M76" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:26</t>
+        </is>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>bahalla</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>bahalla</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>+2.0%</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>+49.8%</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>0.197406338</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>-0.002593662000000024</v>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 2.0% (-31.9% from peak)</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>3M7mbefjcWgW563vCP4f6TBywUBPjENKHnWSA7oxpump</t>
+        </is>
+      </c>
+      <c r="M77" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:32</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Savage Piranha</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>SAVPIR</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>+6.8%</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>+31.9%</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>0.206602759</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>0.006602758999999986</v>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 6.8% (-19.0% from peak)</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>EpZ8FXv6ErRDcC62bHJfTm3BCw1qHYj9ccmuQ6Y4pump</t>
+        </is>
+      </c>
+      <c r="M78" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:36</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Swipe Launchpad</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>SWIPE</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>+13.8%</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>+36.9%</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>0.220034925</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>0.02003492499999998</v>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 13.8% (-16.9% from peak)</t>
+        </is>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>F2CwPY4rV8LMqVMKFr4XzZwf6r2MdnSq8ZXDYPWYpump</t>
+        </is>
+      </c>
+      <c r="M79" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:44:51</t>
+        </is>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>LUMINOUS</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>-57.7%</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>+294.9%</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>-57.7%</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>0.40396155</v>
+      </c>
+      <c r="J80" s="12" t="n">
+        <v>-0.59603845</v>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>trade-event breakeven -57.7%</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>CrZXe59RPAhSaLQYUJc42PrhqGVRERMyPp3ti1UJpump</t>
+        </is>
+      </c>
+      <c r="M80" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:06</t>
+        </is>
+      </c>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Dancing rainbow sperm</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>+8.5%</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>+51.1%</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>0.209794471</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>0.009794470999999999</v>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 8.5% (-28.2% from peak)</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>EwxBSMsJpqw9CawTfPkb71efKB5N9f4cp5KPCtzCpump</t>
+        </is>
+      </c>
+      <c r="M81" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:25</t>
+        </is>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>ferrari meme coin</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>$ferri</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>-17.4%</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>+10.6%</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>-17.4%</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>0.15979234</v>
+      </c>
+      <c r="J82" s="12" t="n">
+        <v>-0.04020766000000001</v>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>trade-event breakeven -17.4%</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>3rG5CZMwYxEpV3Wj6Fo44r8wDhtfHL2oCBBTxNsUpump</t>
+        </is>
+      </c>
+      <c r="M82" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:40</t>
+        </is>
+      </c>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>he made it distributed</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>UNSAID</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>0.193466259</v>
+      </c>
+      <c r="J83" s="12" t="n">
+        <v>-0.00653374100000001</v>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>5pJQVD79S1EyrqpTuavtT4zbFzpufsTMFRAadkYQpump</t>
+        </is>
+      </c>
+      <c r="M83" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:45:45</t>
+        </is>
+      </c>
+      <c r="N83" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>The xAI Quant</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>PudgyWhal3</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
+      <c r="G84" s="9" t="inlineStr"/>
+      <c r="H84" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I84" s="10" t="inlineStr"/>
+      <c r="J84" s="10" t="inlineStr"/>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>6a5yKwmAPS9i9iwNbDsQqNGSW7bteyTZXQirAP9Gpump</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:27</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>JUMP COIN</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>JUMP</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>-35.9%</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>-35.9%</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>0.124005503</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>-0.07599449700000001</v>
+      </c>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -35.9%</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>45HvSv2v2xrGvqmEJddT1iguKnS75kp4o1r2iHF4pump</t>
+        </is>
+      </c>
+      <c r="M85" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:28</t>
+        </is>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Inbox</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>INBOX</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>+15.2%</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>+38.3%</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>0.222825082</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>0.022825082</v>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 15.2% (-16.7% from peak)</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>2WZirfRCJERh3XL3wMADWjkAnXAQTiePaapctNUcpump</t>
+        </is>
+      </c>
+      <c r="M86" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:32</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>DogeWitch</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Halloween</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>0.194215769</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>-0.005784231000000001</v>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.4% after 30s</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>Ah2TBBWL4T9jMdkqNjNq4YfGCRXrcpGAyzGFcBotpump</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:46:42</t>
+        </is>
+      </c>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:47:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>True Volume</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>TVOL</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr"/>
+      <c r="F88" s="9" t="inlineStr"/>
+      <c r="G88" s="9" t="inlineStr"/>
+      <c r="H88" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I88" s="10" t="inlineStr"/>
+      <c r="J88" s="10" t="inlineStr"/>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>qdPaCgwzKC8kpM8YHMZvgFAPtzKzJAd4wDGcxnzpump</t>
+        </is>
+      </c>
+      <c r="M88" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:47:14</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1098,7 +6365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1112,44 +6379,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Mint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:33:45</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Latch</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>LATCH</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK creator-rug-streak rugs=1</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>AicjEWjLZyxKyxbRreUgTdzqEB7ETaCXajePnr2Zpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:31</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Unsaid</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>UNSAID</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK creator-rug-streak rugs=1</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>3W2ovkrGhZiKDV1KbSTSE5MHmCmhSYXyhKFBenqNpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:34:33</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Pute</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Pute</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>98.8303478851977</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>0.26630774616</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 98.83% | 2- Total Locked Liquidity $0 | BLOCK buy-sell-tax 3.95% &gt; 1.00%</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>9276510.922497001</v>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>6rBHUsEs3V8FY6bDqeE7ndMfXHLV3bANidFESKNApump</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+96.3%</t>
+          <t>+93.5%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>18.585317485</v>
+        <v>15.791703366</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>3.585317485000001</v>
+        <v>3.791703366</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,12 +851,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>hdegroott</t>
+          <t>Dust Creek</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>DUST</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>+26.0%</t>
+          <t>+79.6%</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>+103.7%</t>
+          <t>+164.9%</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -883,29 +883,29 @@
         <v>1</v>
       </c>
       <c r="I2" s="12" t="n">
-        <v>1.260472851</v>
+        <v>1.796078826</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>0.2604728510000001</v>
+        <v>0.796078826</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 37.8% (-32.3% from peak, tol=18%)</t>
+          <t>trade-event ratchet-floor 97.8% (locked +100%, peak +165%)</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>6bq9eieXhmzsFj44PH1MiJpe7PXeLqYkkyWCiUMXpump</t>
+          <t>3aoxViYMNPPBnT9HsyHboeGXHqrnLTwwNrLGju5zpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:09</t>
+          <t>2026-10-15 21:52:18</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:14</t>
+          <t>2026-10-15 21:52:22</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>WAKE</t>
+          <t>Neutron Cat</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>WAKE</t>
+          <t>Neutron</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>+47.6%</t>
+          <t>+13.9%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>+114.8%</t>
+          <t>+40.0%</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -947,29 +947,29 @@
         <v>1</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>1.476401498</v>
+        <v>1.139317555</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>0.476401498</v>
+        <v>0.1393175550000001</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 61.9% (-24.6% from peak, tol=18%)</t>
+          <t>trade-event trailing-stop 24.4% (-11.2% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>9FC1KAt2UqjNH1Nrc9MQYmiG2roUFCMRpJ9HwAFXpump</t>
+          <t>CKfFpsXitHUshJhwPfR4SSnpeuEkYEEiJRiYobuKpump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:12</t>
+          <t>2026-10-15 21:52:22</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:13</t>
+          <t>2026-10-15 21:52:24</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>DACITY DOPE</t>
+          <t>Star Mind</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>DADOPE</t>
+          <t>STARMIND</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>+33.4%</t>
+          <t>+72.1%</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>+96.1%</t>
+          <t>+216.5%</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -1011,29 +1011,29 @@
         <v>1</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>1.333973442</v>
+        <v>1.721178712</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>0.333973442</v>
+        <v>0.7211787119999999</v>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 46.0% (-25.6% from peak, tol=18%)</t>
+          <t>watchdog ratchet-floor 89.4% (locked +100%, peak +216%)</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>4jDjvfV3XT5oDduNVhrhyExE89FaD8PgNGHBVcqQpump</t>
+          <t>EZvDXGwfHyRWnAnJo1WHjVUhxpTn2V4kMWmWjh8ypump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:17</t>
+          <t>2026-10-15 21:52:28</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:19</t>
+          <t>2026-10-15 21:52:30</t>
         </is>
       </c>
     </row>
@@ -1043,27 +1043,27 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Grind of solving</t>
+          <t>Star Mind</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Grind</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>-4.2%</t>
+          <t>STARMIND</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>+59.2%</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>+97.8%</t>
+          <t>+115.1%</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -1075,29 +1075,29 @@
         <v>1</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>0.957527534</v>
+        <v>1.592486587</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>-0.04247246599999999</v>
+        <v>0.592486587</v>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 4.2% (locked +25%, peak +98%)</t>
+          <t>trade-event trailing-stop 74.9% (-18.7% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>J9GjSReXKUw2hfp98s4WT2xnESByYD5rAvHhwAYupump</t>
+          <t>7bPjdagW25phmm2gcSpXknX2r7NnEsQYDaKwvszppump</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:19</t>
+          <t>2026-10-15 21:52:48</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:22</t>
+          <t>2026-10-15 21:52:48</t>
         </is>
       </c>
     </row>
@@ -1107,43 +1107,63 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>TESLA ROADSTER</t>
+          <t xml:space="preserve">dipcat </t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>ROADSTER</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>dipcat</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>+21.5%</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>+48.2%</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
+      <c r="I6" s="12" t="n">
+        <v>1.215159946</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0.215159946</v>
+      </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog trailing-stop 32.8% (-10.4% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>4knqVYwrzkKb5LATvzPVB6SF8eqtSvAzHPUugzMEpump</t>
+          <t>FQF7Hu3Y5ZyzZ4WwXFDPCeXYJaqrJvrxCxg2gwYopump</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:22</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr"/>
+          <t>2026-10-15 21:52:49</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:52:53</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1151,12 +1171,12 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Jason Caston</t>
+          <t>Higher (Again)</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>JASONCASTO</t>
+          <t>HIGHER</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -1166,12 +1186,12 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>+15.0%</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -1183,29 +1203,29 @@
         <v>1</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>0.956158821</v>
+        <v>0.94368732</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>-0.04384117899999995</v>
+        <v>-0.05631268</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 0.8% after 30s</t>
+          <t>trade-event trailing-stop 2.7% (-10.7% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>AzDRnv5uU6zEwG7NrQpYdrUWPndSX7YKMSuT3hh4pump</t>
+          <t>4ynDkdW7kWPcbHLTeVGwjisskeCH9n5sNjWh231Qpump</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:29</t>
+          <t>2026-10-15 21:52:52</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:59</t>
+          <t>2026-10-15 21:52:53</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1235,12 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Gravik</t>
+          <t>StarMind</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Gravik</t>
+          <t>SI1</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1230,12 +1250,12 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+4.9%</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>+28.8%</t>
+          <t>+80.3%</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1247,29 +1267,29 @@
         <v>1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1.02030306</v>
+        <v>1.049157216</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0.02030306000000004</v>
+        <v>0.049157216</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 11.2% (-13.7% from peak, tol=10%)</t>
+          <t>trade-event ratchet-floor 14.4% (locked +25%, peak +80%)</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>3tASaZkP3hHgZAEK8jWvz97v5W5rrkNKtPBFUVYbpump</t>
+          <t>6ke5Gtdd3247WUfprfkUn9fuofrJZXP3knPxEXeRpump</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:32</t>
+          <t>2026-10-15 21:53:03</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:42</t>
+          <t>2026-10-15 21:53:05</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1299,12 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Lattice</t>
+          <t>hdegroott</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>LATTICE</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1307,12 +1327,12 @@
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>EFxUdbaYwiAq3wvd4YzUNpDp47sFVHknnGDZLV3opump</t>
+          <t>4yZuUfpwv46CmijuKrnNut98d7NZfrYivaiRRoC1pump</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:39</t>
+          <t>2026-10-15 21:53:12</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr"/>
@@ -1323,63 +1343,43 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>DaemonFi</t>
+          <t>tttttttttttttttttt</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>DAEMON</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>+10.7%</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>ttttttttttttt</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
       <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>1.003860707</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>0.003860707000000074</v>
-      </c>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 9.3% after 30s</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>2Bn1aWe8uFQHe3WUebZN223QNkTZvLCeE1xRCziRpump</t>
+          <t>BDStHaH3DyT8RmBsQtot6c3LRYS9vxA7nF9uP3JDpump</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:46</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:45:16</t>
-        </is>
-      </c>
+          <t>2026-10-15 21:53:20</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>hdegroott</t>
+          <t>QUENTRA</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>QUENTRA</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>+26.0%</t>
+          <t>+55.3%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>+85.5%</t>
+          <t>+123.8%</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -1419,29 +1419,29 @@
         <v>1</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1.260472851</v>
+        <v>1.552873369</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>0.2604728510000001</v>
+        <v>0.5528733690000001</v>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 37.8% (-25.7% from peak, tol=18%)</t>
+          <t>watchdog trailing-stop 70.5% (-23.8% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>FKTUBvsC3mzYWKGkRa3iMtDzZQcqxE3HgrHWN2sWpump</t>
+          <t>3h4poyYGABrfoRBMzD11sF5fuLq1hvGZpNdtoeQfpump</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:48</t>
+          <t>2026-10-15 21:53:25</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:52</t>
+          <t>2026-10-15 21:53:26</t>
         </is>
       </c>
     </row>
@@ -1451,63 +1451,43 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Grind of solving</t>
+          <t>HIGHER</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>GOS</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>-3.8%</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>+41.0%</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>HIGHER</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
       <c r="H12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>0.961785957</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>-0.03821404299999998</v>
-      </c>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 4.7% (-25.7% from peak, tol=10%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>7mR1HNeE4nEpKxC1EWuUdyAZqpws5oHUaeAQ9oHTpump</t>
+          <t>CpDVpoJj6oaLrsUNLUUgCi9BPRRxRv1cXkswqASXpump</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:50</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:44:50</t>
-        </is>
-      </c>
+          <t>2026-10-15 21:53:34</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -1515,63 +1495,43 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>clout</t>
+          <t>Flowchart Fun</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>CLOUT</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>+51.4%</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>+181.7%</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>Flowchart Fun</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
       <c r="H13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>1.514361118</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>0.5143611180000001</v>
-      </c>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>watchdog ratchet-floor 66.2% (locked +100%, peak +182%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>2akqEiYYuaQaG8Yx7M2xcj5yaGwNniFuxc37PLCCpump</t>
+          <t>BSXmsZaJMwti9yQjw35dsKKFfm8FPt57Dc9mi2m3pump</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:57</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:44:58</t>
-        </is>
-      </c>
+          <t>2026-10-15 21:53:39</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -1579,63 +1539,43 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>The Finance Eagle</t>
+          <t>Rejects SOL</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Benji</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>+69.2%</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>+190.5%</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>GAYJEZ</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr"/>
       <c r="H14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>1.69178798</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>0.69178798</v>
-      </c>
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>watchdog ratchet-floor 86.1% (locked +100%, peak +191%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>7zfmvaEc4YSmAQFoQmEjtsdZGm9kvJPJLtLXFwZ1pump</t>
+          <t>9362QfuQWxNN4ZorYpJP5jbXuLJb8E8bwic5u67rpump</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:58</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:45:01</t>
-        </is>
-      </c>
+          <t>2026-10-15 21:53:40</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -1643,43 +1583,63 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>QuantumTEK</t>
+          <t>Deepnets</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>QTEK</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
+          <t>DNET</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>+19.9%</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>+49.7%</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
+      <c r="I15" s="12" t="n">
+        <v>1.199019756</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0.199019756</v>
+      </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog trailing-stop 31.0% (-12.5% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>BYjrG1AaCtVBr57RbARR9Bx2bfPTuFJdmz9Q3J8xpump</t>
+          <t>59DdoxHXCKzxPjqXSAH1j41gfqZf3isg5iipTJgPpump</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:00</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="inlineStr"/>
+          <t>2026-10-15 21:53:42</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:53:44</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -1687,27 +1647,27 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>ONNASCH</t>
+          <t>Tokenization</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>ONNASCH</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>-3.2%</t>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>+63.4%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>+97.6%</t>
+          <t>+169.3%</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -1719,29 +1679,29 @@
         <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.968375264</v>
+        <v>1.634041562</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>-0.03162473600000004</v>
+        <v>0.6340415619999999</v>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 5.4% (locked +25%, peak +98%)</t>
+          <t>watchdog ratchet-floor 79.6% (locked +100%, peak +169%)</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>638B3vPou64nGKEtGdj7rZDiGyiKgi4e8Vmnund8pump</t>
+          <t>5ssFLsPvrvrUzYznka2ReAeXufQhWJyviQYNhVs6pump</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:04</t>
+          <t>2026-10-15 21:53:56</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:04</t>
+          <t>2026-10-15 21:53:58</t>
         </is>
       </c>
     </row>
@@ -1751,27 +1711,27 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Grind of solving</t>
+          <t>Tokenization</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>GOS</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>+68.1%</t>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>+187.7%</t>
+          <t>+74.2%</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1783,29 +1743,29 @@
         <v>1</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>1.680943238</v>
+        <v>0.92176152</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>0.680943238</v>
+        <v>-0.07823848</v>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>watchdog ratchet-floor 84.9% (locked +100%, peak +188%)</t>
+          <t>trade-event ratchet-floor 0.3% (locked +25%, peak +74%)</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>2kx5si36meV8Nq5fWp8hnkj13cGygwqGo7vUHLEfpump</t>
+          <t>6zBJkALg7QAHWqPc9TfbDCHcoXmaLSdV3G6RjaYXpump</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:05</t>
+          <t>2026-10-15 21:54:17</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:06</t>
+          <t>2026-10-15 21:54:18</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1775,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>PixelGO</t>
+          <t>TamperMonkey</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>PIXELGO</t>
+          <t>TAMPERMONKEY</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -1843,12 +1803,12 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>7tQei4v3NRQ2Jax9bJkrR5yFR8bNkxndqLuWBz34pump</t>
+          <t>GmhxbgXNGXLpwc52kwnqtW2Ey6Yp4qJsLzAExn6Jpump</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:21</t>
+          <t>2026-10-15 21:54:23</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr"/>
@@ -1859,63 +1819,43 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>The Finance Eagle</t>
+          <t>Tokenization</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Benji</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>+42.8%</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>+135.5%</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
       <c r="H19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>1.427546782</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>0.4275467820000001</v>
-      </c>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 56.5% (-33.6% from peak, tol=18%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>3Vr1VPpKcrvKwNWPs7b1jRGpGaVm2ws4wdfeumDzpump</t>
+          <t>2FE6iUZq379QScSKMf55a5L7m4tYe5oErtzA7oQvpump</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:26</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:45:29</t>
-        </is>
-      </c>
+          <t>2026-10-15 21:54:29</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -1923,12 +1863,12 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Worst</t>
+          <t>Agent wif Anxiety</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>WORST</t>
+          <t>ANXIETY</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1938,12 +1878,12 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>+72.3%</t>
+          <t>+24.6%</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -1955,34 +1895,78 @@
         <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>1.071346382</v>
+        <v>1.026940997</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>0.07134638199999999</v>
+        <v>0.02694099700000008</v>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>watchdog ratchet-floor 16.8% (locked +25%, peak +72%)</t>
+          <t>watchdog trailing-stop 11.9% (-10.2% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>5Zbn8UDvCzGQ9YYdxv4tx4GExxWdVV1yjvu7fzBFpump</t>
+          <t>D9aqQJGJBW28KNyBxorD5kJdZPjjjWdbWSiXJC2Kpump</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:40</t>
+          <t>2026-10-15 21:54:31</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:42</t>
-        </is>
-      </c>
+          <t>2026-10-15 21:54:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Made By Humans On Earth</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>EARTH</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>9T8DRSm4F5JbDuCTQcZhHfvcDpB8g3UenSYxnXj1pump</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:54:39</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:N21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1993,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2051,17 +2035,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:24</t>
+          <t>2026-10-15 21:52:31</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Preorder</t>
+          <t>Spurdo</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>PREORDER</t>
+          <t>Spurdo</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
@@ -2072,7 +2056,7 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=21 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=8 &gt; 5</t>
         </is>
       </c>
       <c r="G2" s="18" t="n">
@@ -2080,96 +2064,96 @@
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>7XxKcFW46jmg5wRQu2aMyQtx59snFU8AKmNRStrxpump</t>
+          <t>7qiEqkHWzZgiAMaKD4dBX1VQ83ymPPF6k7wGUBhCpump</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>2026-10-15 21:44:38</t>
+          <t>2026-10-15 21:52:50</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Real Wallet</t>
+          <t>Bonjour dog</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>REALWALLET</t>
+          <t>BONJOURDOG</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>135.291892573446</v>
+        <v>88.82805794339038</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>0</v>
+        <v>286.20237205479</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=22 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 88.83% | 2- Total Locked Liquidity $286 | BLOCK sniper-bundle 10 wallets besides LP</t>
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0</v>
+        <v>29908737.786261</v>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>7gwit2ACGNhgfsDQPFfGYRW1xAf1Q6rQVwjruCzspump</t>
+          <t>5Db9vmVE3vb8H2XDGH52E63iFngrVE86hPcu8wxtpump</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:01</t>
+          <t>2026-10-15 21:52:58</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Archer Exchange</t>
+          <t>Gold Walkman</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>ARCHER</t>
+          <t>GW</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>73.85057040173736</v>
+        <v>135.291892573446</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>762.1833265741201</v>
+        <v>0</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 73.85% | 2- Total Locked Liquidity $762 | BLOCK sniper-bundle 10 wallets besides LP</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=12 &gt; 5</t>
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>32641376.905863</v>
+        <v>0</v>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>DLKZSpwBVhpk8TUseUShGJXW8TSkDVZRUETNky7mhfNn</t>
+          <t>3gin6jyt8HKizqfofCfMs9EfPeo5WEwWUepx1dYgpump</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>2026-10-15 21:45:15</t>
+          <t>2026-10-15 21:53:24</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>The Finance Eagle</t>
+          <t>Jean Cul</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Benji</t>
+          <t>Cul</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
@@ -2180,7 +2164,7 @@
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=6 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=17 &gt; 5</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
@@ -2188,43 +2172,7 @@
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>D6eLPCHLd8wuMQ8ykwPeMFgSz5iTQLLLUasHCYoKpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:45:29</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Benji The Eagle</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>BENJI</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>135.291892573446</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=23 &gt; 5</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>7mPmuUEEh3Y3dxAbKyb5EgYtFgFRtrYJ2oDscvG1pump</t>
+          <t>EAJ1auhSGyoFBpugVindEjWNHnSrqbzczfmNBZbCpump</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -670,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+93.5%</t>
+          <t>+118.2%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>15.791703366</v>
+        <v>22.10382535</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>3.791703366</v>
+        <v>7.103825350000001</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1307,22 +1307,38 @@
           <t>Hugo</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>+243.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>+456.7%</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
+      <c r="I9" s="12" t="n">
+        <v>3.42975081</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>2.42975081</v>
+      </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 284.1% (-31.0% from peak, tol=28%)</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
@@ -1335,7 +1351,11 @@
           <t>2026-10-15 21:53:12</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:56:45</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -1965,8 +1985,180 @@
       </c>
       <c r="N21" s="10" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Jeet Slapper</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>JSLAP</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>+4.2%</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>+9.8%</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>1.041772817</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>0.04177281700000002</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 9.8% after 30s</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>AjD35QUtwy6NieqkkAKKNacfzQVvdh47BR6pHr6Xpump</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:56:55</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:57:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Launch on Moat</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>MOAT</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>+84.1%</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>+184.7%</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>1.840598357</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0.840598357</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 102.8% (-28.8% from peak, tol=28%)</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>7bmhZEWfmGzrJC3xuK4pfUWrgzo1ymQ9X6wxzFPypump</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:57:48</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Official NeymarJr. Token</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>NEYMAR</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>EN37FBT9sApUgGMtLiGmYEESR1E6JjqowidyQTF2pump</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:57:52</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N21"/>
+  <autoFilter ref="A1:N24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -37,16 +37,16 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,17 +67,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,15 +107,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -131,10 +131,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -623,7 +626,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +636,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +646,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -664,7 +667,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -676,7 +679,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+29.7%</t>
         </is>
       </c>
     </row>
@@ -698,8 +701,8 @@
           <t>Total invested (SOL)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>0</v>
+      <c r="B19" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -708,8 +711,8 @@
           <t>Total back (SOL)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>0</v>
+      <c r="B20" s="4" t="n">
+        <v>1.006577783</v>
       </c>
     </row>
     <row r="21">
@@ -719,7 +722,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0</v>
+        <v>0.006577783000000004</v>
       </c>
     </row>
     <row r="22">
@@ -845,43 +848,63 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>LOFI</t>
+          <t>bum</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>LOFI</t>
+          <t>bum</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>+29.7%</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
+      <c r="I2" s="12" t="n">
+        <v>1.006577783</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>0.006577783000000004</v>
+      </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog trailing-stop 9.6% (-15.5% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>EaCzZRVGhdBL9VsAwui7Wc8pSUqMz97Ht4PsWoLQpump</t>
+          <t>23tZw1ZMsRG2ZVWzBNWqFS8BCkNXcVyJcbt5ckakpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:41</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr"/>
+          <t>2026-10-16 00:53:13</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:16</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -889,20 +912,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Cash Cat</t>
+          <t>PuzunSync</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>BLACKIE</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+          <t>PUZUN</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr"/>
       <c r="F3" s="9" t="inlineStr"/>
       <c r="G3" s="9" t="inlineStr"/>
       <c r="H3" s="12" t="n">
@@ -917,12 +940,12 @@
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>63AJe8VZuQ9JbQc6L1JAwFZLQmxEovihVJmL4ucnpump</t>
+          <t>BExLBBVqk4mVVyU1GMk8Y9ZK5k8hCAefpoPgocKppump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:49</t>
+          <t>2026-10-16 00:53:22</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr"/>
@@ -931,14 +954,22 @@
       <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr"/>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>OBSIDIAN</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="9" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
       <c r="H4" s="12" t="n">
@@ -953,12 +984,12 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>43ePcpnkHoE4yXhaq5e9uQTdxGqNrzwam1AhDqk9pump</t>
+          <t>4waSCsC6ppAxjAgVcLCiSVRX5L1Qv1zqTvAKkstkpump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:51</t>
+          <t>2026-10-16 00:53:24</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr"/>
@@ -989,80 +1020,80 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>2026-10-15 22:00:47</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>First Responders Coin</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>FRC</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="n">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:15</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Microducks</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>MICRODUCKS</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
         <v>135.291892573446</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=13 &gt; 5</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="n">
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=12 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t>GiUgf9yEPfQXhgCnX9pVvJgiQYbfUcPosg8uxMCSpump</t>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>FCUbf4HHAdGwrJpzmDT7PJfWWzuYqAyEwkGZLP6ypump</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,12 +45,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="6">
@@ -107,14 +107,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -132,6 +132,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -616,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -626,7 +629,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -646,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -679,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+29.7%</t>
+          <t>+79.5%</t>
         </is>
       </c>
     </row>
@@ -702,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -712,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1.006577783</v>
+        <v>4.823946429</v>
       </c>
     </row>
     <row r="21">
@@ -722,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.006577783000000004</v>
+        <v>0.8239464290000003</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -964,38 +967,318 @@
           <t>OBSIDIAN</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>+10.6%</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>+42.9%</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
+      <c r="I4" s="12" t="n">
+        <v>1.106062846</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>0.1060628459999999</v>
+      </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
+          <t>trade-event trailing-stop 20.7% (-15.6% from peak, tol=10%)</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>4waSCsC6ppAxjAgVcLCiSVRX5L1Qv1zqTvAKkstkpump</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:24</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>MSCI官网：经非营运公司</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>MSCI官网：</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
           <t>holding</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>4waSCsC6ppAxjAgVcLCiSVRX5L1Qv1zqTvAKkstkpump</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:24</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>EqTr7549SQmGsUGVpJtQFabvZdedcbjP1yxbvhj7ittv</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:26</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>NOSTRATEGY</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>NSTR</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>+74.3%</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>+161.0%</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>1.743007023</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0.7430070230000001</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>trade-event ratchet-floor 91.8% (locked +100%, peak +161%)</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>8VgfKMmCYA3JxnzFD876Up9Rsiesf6zcmYPxiotdpump</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:27</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>krrby</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>krrby</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>krrb2QFwEQSYYvKGpEizwS63p5S5EMcUoS5UT812rjt</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:30</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>OFFICIAL NEYMAR JR</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>NEYMAR</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>A26Bz38Yag5uPM1EEbnBnSCMC1TrApNmuPQpddPnpump</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:33</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>MicroStrategy</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>-3.2%</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>+84.4%</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.968298777</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>-0.031701223</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>trade-event ratchet-floor 5.4% (locked +25%, peak +84%)</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>7tm1TXFgaNRtFxU3rsfT2fSqDKMArmwFKMWftQr6pump</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:44</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:45</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1020,78 +1303,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>2026-10-16 00:53:15</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Microducks</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>MICRODUCKS</t>
         </is>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>135.291892573446</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=12 &gt; 5</t>
         </is>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>FCUbf4HHAdGwrJpzmDT7PJfWWzuYqAyEwkGZLP6ypump</t>
         </is>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,14 +37,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C5700"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="009C0006"/>
     </font>
     <font>
@@ -52,8 +44,12 @@
       <color rgb="001F4E79"/>
       <sz val="16"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,17 +63,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,14 +98,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -131,16 +122,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +621,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +631,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -670,7 +652,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +664,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+79.5%</t>
+          <t>+108.9%</t>
         </is>
       </c>
     </row>
@@ -694,7 +676,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-2.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +687,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +697,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>4.823946429</v>
+        <v>0.979319382</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +707,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.8239464290000003</v>
+        <v>-0.02068061799999998</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,434 +833,66 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>bum</t>
+          <t>SATINU</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>bum</t>
+          <t>SATINU</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>WON</t>
+          <t>LOST</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>+29.7%</t>
+          <t>+108.9%</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="12" t="n">
-        <v>1.006577783</v>
+        <v>0.979319382</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>0.006577783000000004</v>
+        <v>-0.02068061799999998</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 9.6% (-15.5% from peak, tol=10%)</t>
+          <t>watchdog breakeven -2.1%</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>23tZw1ZMsRG2ZVWzBNWqFS8BCkNXcVyJcbt5ckakpump</t>
+          <t>Cw3TfKqnvnsMGdYVm4kMFiowb2K5XXmR2vXYTxudpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:13</t>
+          <t>2026-10-16 03:18:45</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>PuzunSync</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>PUZUN</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr"/>
-      <c r="F3" s="9" t="inlineStr"/>
-      <c r="G3" s="9" t="inlineStr"/>
-      <c r="H3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>BExLBBVqk4mVVyU1GMk8Y9ZK5k8hCAefpoPgocKppump</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:22</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Obsidian</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>OBSIDIAN</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>+10.6%</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>+42.9%</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="12" t="n">
-        <v>1.106062846</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>0.1060628459999999</v>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>trade-event trailing-stop 20.7% (-15.6% from peak, tol=10%)</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>4waSCsC6ppAxjAgVcLCiSVRX5L1Qv1zqTvAKkstkpump</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:24</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>MSCI官网：经非营运公司</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>MSCI官网：</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>EqTr7549SQmGsUGVpJtQFabvZdedcbjP1yxbvhj7ittv</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:26</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>NOSTRATEGY</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>NSTR</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>+74.3%</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>+161.0%</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="12" t="n">
-        <v>1.743007023</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>0.7430070230000001</v>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>trade-event ratchet-floor 91.8% (locked +100%, peak +161%)</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>8VgfKMmCYA3JxnzFD876Up9Rsiesf6zcmYPxiotdpump</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:27</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>krrby</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>krrby</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>krrb2QFwEQSYYvKGpEizwS63p5S5EMcUoS5UT812rjt</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:30</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>OFFICIAL NEYMAR JR</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>NEYMAR</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>A26Bz38Yag5uPM1EEbnBnSCMC1TrApNmuPQpddPnpump</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:33</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>MicroStrategy</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>-3.2%</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>+84.4%</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>0.968298777</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>-0.031701223</v>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>trade-event ratchet-floor 5.4% (locked +25%, peak +84%)</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>7tm1TXFgaNRtFxU3rsfT2fSqDKMArmwFKMWftQr6pump</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:44</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:45</t>
+          <t>2026-10-16 03:18:46</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1289,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1303,80 +917,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Mint</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:15</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>Microducks</t>
-        </is>
-      </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>MICRODUCKS</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>135.291892573446</v>
-      </c>
-      <c r="E2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=12 &gt; 5</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="16" t="inlineStr">
-        <is>
-          <t>FCUbf4HHAdGwrJpzmDT7PJfWWzuYqAyEwkGZLP6ypump</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +37,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -48,8 +48,12 @@
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,12 +67,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,8 +114,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -601,7 +610,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +620,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -641,7 +650,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -664,7 +673,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+108.9%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -676,7 +685,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -686,8 +695,8 @@
           <t>Total invested (SOL)</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>1</v>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -696,8 +705,8 @@
           <t>Total back (SOL)</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>0.979319382</v>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -707,7 +716,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>-0.02068061799999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -736,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -833,66 +842,90 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>SATINU</t>
+          <t>Meme Index 100</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>SATINU</t>
+          <t>MEME100</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>-2.1%</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>+108.9%</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>-2.1%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr"/>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="12" t="n">
-        <v>0.979319382</v>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>-0.02068061799999998</v>
-      </c>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>watchdog breakeven -2.1%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>Cw3TfKqnvnsMGdYVm4kMFiowb2K5XXmR2vXYTxudpump</t>
+          <t>YsALHbPSQkSu53AQsAKCxKFVknAPpJ8Vr58GoyNpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:18:45</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 03:18:46</t>
-        </is>
-      </c>
+          <t>2026-10-16 03:31:49</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Rankz</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>RANKZ</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr"/>
+      <c r="F3" s="9" t="inlineStr"/>
+      <c r="G3" s="9" t="inlineStr"/>
+      <c r="H3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>7d8W2JerSognHYeBAtcg2RaJs97rccUkAbR8KTVhpump</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:31:51</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,16 +37,16 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,15 +107,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -130,6 +130,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -610,7 +613,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -630,7 +633,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -640,7 +643,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -661,7 +664,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -673,7 +676,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+26.7%</t>
         </is>
       </c>
     </row>
@@ -695,8 +698,8 @@
           <t>Total invested (SOL)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>0</v>
+      <c r="B19" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -705,8 +708,8 @@
           <t>Total back (SOL)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>0</v>
+      <c r="B20" s="4" t="n">
+        <v>1.002599381</v>
       </c>
     </row>
     <row r="21">
@@ -716,7 +719,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0</v>
+        <v>0.002599381000000012</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -842,43 +845,63 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Meme Index 100</t>
+          <t>VEILTROLL</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>MEME100</t>
+          <t>VEILTROLL</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>+0.3%</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>+26.7%</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
+      <c r="I2" s="12" t="n">
+        <v>1.002599381</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>0.002599381000000012</v>
+      </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog trailing-stop 0.3% (-20.9% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>YsALHbPSQkSu53AQsAKCxKFVknAPpJ8Vr58GoyNpump</t>
+          <t>ocQkotYQjj1jzVqq3ZyZtL4oRXcLK6zMuwLXqWRpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:31:49</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:39:52</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:39:54</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -886,20 +909,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Rankz</t>
+          <t>Grokazon</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>RANKZ</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+          <t>GZON</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr"/>
       <c r="F3" s="9" t="inlineStr"/>
       <c r="G3" s="9" t="inlineStr"/>
       <c r="H3" s="12" t="n">
@@ -914,18 +937,62 @@
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>7d8W2JerSognHYeBAtcg2RaJs97rccUkAbR8KTVhpump</t>
+          <t>8LwcuvF6drQ21pmhZm1qGZBdeLkLGHx2q9XHDV65pump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:31:51</t>
+          <t>2026-10-16 04:39:54</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>rivaly.fun</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>RIVALY</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr"/>
+      <c r="G4" s="9" t="inlineStr"/>
+      <c r="H4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>6N22dmEVa9Ky8ezvhm5FvCtTpFgd9fLBuSW9wSmwpump</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:39:55</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -950,42 +1017,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,16 +41,16 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="6">
@@ -72,12 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,14 +107,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -134,7 +134,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -613,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +629,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -653,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -664,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -676,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+25.4%</t>
         </is>
       </c>
     </row>
@@ -688,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-1.4%</t>
         </is>
       </c>
     </row>
@@ -699,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -709,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1.002599381</v>
+        <v>6.460753118</v>
       </c>
     </row>
     <row r="21">
@@ -719,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.002599381000000012</v>
+        <v>0.4607531180000004</v>
       </c>
     </row>
     <row r="22">
@@ -748,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -919,20 +925,36 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr"/>
-      <c r="F3" s="9" t="inlineStr"/>
-      <c r="G3" s="9" t="inlineStr"/>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>+7.4%</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="H3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
+      <c r="I3" s="12" t="n">
+        <v>0.991037663</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>-0.008962337000000042</v>
+      </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog breakeven -0.9%</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
@@ -945,7 +967,11 @@
           <t>2026-10-16 04:39:54</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:39:56</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
@@ -963,36 +989,512 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>-7.0%</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>-7.0%</t>
+        </is>
+      </c>
       <c r="H4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
+      <c r="I4" s="12" t="n">
+        <v>0.930309045</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>-0.069690955</v>
+      </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
+          <t>watchdog stop-loss -7.0%</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>6N22dmEVa9Ky8ezvhm5FvCtTpFgd9fLBuSW9wSmwpump</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:39:55</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:39:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Toly $1 Coin</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
           <t>holding</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>6N22dmEVa9Ky8ezvhm5FvCtTpFgd9fLBuSW9wSmwpump</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:39:55</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>2dwa82kTNo8MXvj3K8wZqsx79h97pTXC2nCAfTkYpump</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:10</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Flying tesla skyster</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>3njQBDXmF4Z97u5BJzAzBRuMTMA89N3942i65pdLpump</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:13</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Baton Man</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>BatonMan</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>+30.1%</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+48.5%</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>1.300951674</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.300951674</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 30.1% (-12.4% from peak, tol=10%)</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>8f6htt8WT2qGau2T7MBXMW9NJXpcfFhTetdrcS2Rpump</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:17</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Ava Larps</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>95yf3XvjpTzJfWAcqqvXhH5s4DS55tY1tiJ1iR9qpump</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:24</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>ТamPad</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>ТamPad</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>DiGYfgNSzYsvN4zbjZa6NyjyNE95X2qkV32ML5thpump</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:51</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>ТamPad</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>ТamPad</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>0.981940087</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>-0.01805991299999998</v>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin -0.8% after 30s</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>FppJ8swha44WggXN2UG9mTKG1b35ACBUYhvMsdKWpump</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:56</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:41:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>amor</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>amor</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>+25.4%</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>+69.8%</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>1.253915268</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.2539152680000001</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 25.4% (-26.2% from peak, tol=18%)</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>HuDj7pNgAcVXb7cEtPXJEQTqVQGQGkuHBTh7Djsopump</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:41:19</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:41:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>TESCREAL</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>TESCREAL</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>NZZY9SnqrMLHiHxoqnstLCsF7Lmr1rGF1Ba3HAEpump</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:41:25</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>DRAINLOVE</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>DRAINLOVE</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>9HmC4jXxkaFchQHQEy873oA3bCcpGziz1hW7aP14pump</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:41:34</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1003,7 +1505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1017,44 +1519,188 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Mint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:39:57</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>SUPER INU</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>SINU</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>3.319804998249779</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>7919.615246532211</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 3.32% | 2- Total Locked Liquidity $7.9K | BLOCK insider-whale 763,701,068 tokens (&gt;= 100,000,000); concentrated-holder 76.4% &gt;= 30%</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>763701067.612466</v>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>3szhHxoagYbDNEEj35cmBxKr3iadFLrrSVyjjuwapump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:12</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Phase Punk</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>PHASEPUNK</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=15 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>9KGZuyJ8UXokgREBFxGguA1hVVdUmBYwtTSaQbPMpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:19</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Up Side Down Tesla</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK clone-ticker USDT; serial-deployer launches=38 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>7vG48c29W1oAtAeUUpphLgQ2bDUWTiXokhrYF2zsX34p</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:41</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>niggi</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>niggi</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=6 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>3o1kTH57F6kuuhjcpMSuggQHRjxmThEri3iGnPXfpump</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,11 +37,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,9 +113,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -138,9 +138,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+25.4%</t>
+          <t>+72.7%</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-2.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>6.460753118</v>
+        <v>2.202809591</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.4607531180000004</v>
+        <v>0.2028095909999998</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,61 +851,61 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>VEILTROLL</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>VEILTROLL</t>
+          <t>OKAY</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>WON</t>
+          <t>LOST</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+76.9%</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="12" t="n">
-        <v>1.002599381</v>
+        <v>0.958761799</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>0.002599381000000012</v>
+        <v>-0.04123820099999997</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 0.3% (-20.9% from peak, tol=10%)</t>
+          <t>trade-event breakeven -4.1%</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>ocQkotYQjj1jzVqq3ZyZtL4oRXcLK6zMuwLXqWRpump</t>
+          <t>GHnGviuMzqMoBx8NuZNN3X5QDkYA7mZBu3xVGoPNmVzT</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:39:52</t>
+          <t>2026-10-16 04:50:24</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:39:54</t>
+          <t>2026-10-16 04:50:25</t>
         </is>
       </c>
     </row>
@@ -915,61 +915,61 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Grokazon</t>
+          <t>Flying Tesla Roadster 2.0</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>GZON</t>
+          <t>FTR</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>LOST</t>
+          <t>WON</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>+24.4%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+68.5%</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="H3" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>0.991037663</v>
+        <v>1.244047792</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>-0.008962337000000042</v>
+        <v>0.2440477919999999</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>watchdog breakeven -0.9%</t>
+          <t>trade-event ratchet-floor 24.4% (locked +25%, peak +68%)</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>8LwcuvF6drQ21pmhZm1qGZBdeLkLGHx2q9XHDV65pump</t>
+          <t>J5s6eTHv3ZhzG5X4LrEwbr1LgRoj5tSmsZDrxntMpump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:39:54</t>
+          <t>2026-10-16 04:50:29</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:39:56</t>
+          <t>2026-10-16 04:50:31</t>
         </is>
       </c>
     </row>
@@ -979,63 +979,43 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>rivaly.fun</t>
+          <t>numen.cash</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>RIVALY</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>-7.0%</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>-7.0%</t>
-        </is>
-      </c>
+          <t>NUMEN</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr"/>
+      <c r="G4" s="9" t="inlineStr"/>
       <c r="H4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="12" t="n">
-        <v>0.930309045</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>-0.069690955</v>
-      </c>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>watchdog stop-loss -7.0%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>6N22dmEVa9Ky8ezvhm5FvCtTpFgd9fLBuSW9wSmwpump</t>
+          <t>GvEjB2Z24Hbq3Tf3F5e5vPgBpmV5p7YnL4SLDpoapump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:39:55</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:39:56</t>
-        </is>
-      </c>
+          <t>2026-10-16 04:50:31</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -1043,12 +1023,12 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Toly $1 Coin</t>
+          <t>p-null.si</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>p(null)</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -1071,12 +1051,12 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>2dwa82kTNo8MXvj3K8wZqsx79h97pTXC2nCAfTkYpump</t>
+          <t>DuQU1Fi4KmT4cQgn1k1QYkqtYVEMRhEXbdijsipypump</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:40:10</t>
+          <t>2026-10-16 04:50:37</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr"/>
@@ -1087,12 +1067,12 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Flying tesla skyster</t>
+          <t>Cuck Coding</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>FTS</t>
+          <t>Cuck</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -1115,386 +1095,18 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>3njQBDXmF4Z97u5BJzAzBRuMTMA89N3942i65pdLpump</t>
+          <t>4RrzBXWpbXbSsTNHxDxEjffrSzuG4HPoSLwPr7yVpump</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:40:13</t>
+          <t>2026-10-16 04:50:41</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Baton Man</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>BatonMan</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>+30.1%</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>+48.5%</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>1.300951674</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>0.300951674</v>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 30.1% (-12.4% from peak, tol=10%)</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>8f6htt8WT2qGau2T7MBXMW9NJXpcfFhTetdrcS2Rpump</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:17</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Ava Larps</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Ava</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>95yf3XvjpTzJfWAcqqvXhH5s4DS55tY1tiJ1iR9qpump</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:24</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>ТamPad</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>ТamPad</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>DiGYfgNSzYsvN4zbjZa6NyjyNE95X2qkV32ML5thpump</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:51</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>ТamPad</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>ТamPad</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>-1.8%</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>0.981940087</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>-0.01805991299999998</v>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>watchdog dead-coin -0.8% after 30s</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>FppJ8swha44WggXN2UG9mTKG1b35ACBUYhvMsdKWpump</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:56</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:41:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>amor</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>amor</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>+25.4%</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>+69.8%</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>1.253915268</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.2539152680000001</v>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 25.4% (-26.2% from peak, tol=18%)</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>HuDj7pNgAcVXb7cEtPXJEQTqVQGQGkuHBTh7Djsopump</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:41:19</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:41:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>TESCREAL</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>TESCREAL</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>NZZY9SnqrMLHiHxoqnstLCsF7Lmr1rGF1Ba3HAEpump</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:41:25</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>DRAINLOVE</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>DRAINLOVE</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr"/>
-      <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="10" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>9HmC4jXxkaFchQHQEy873oA3bCcpGziz1hW7aP14pump</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:41:34</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N13"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1505,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1563,144 +1175,36 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:39:57</t>
+          <t>2026-10-16 04:50:34</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>SUPER INU</t>
+          <t>Flying Tesla Roadster 2.0</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>SINU</t>
+          <t>FTR2,0</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>3.319804998249779</v>
+        <v>80.87747102079877</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>7919.615246532211</v>
+        <v>521.0370369380399</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 3.32% | 2- Total Locked Liquidity $7.9K | BLOCK insider-whale 763,701,068 tokens (&gt;= 100,000,000); concentrated-holder 76.4% &gt;= 30%</t>
+          <t>1- Liquidity (LP tokens) Locked 80.88% | 2- Total Locked Liquidity $521 | BLOCK insider-whale 151,660,777 tokens (&gt;= 100,000,000)</t>
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>763701067.612466</v>
+        <v>151660777.334045</v>
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>3szhHxoagYbDNEEj35cmBxKr3iadFLrrSVyjjuwapump</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:12</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Phase Punk</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>PHASEPUNK</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="n">
-        <v>135.291892573446</v>
-      </c>
-      <c r="E3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=15 &gt; 5</t>
-        </is>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>9KGZuyJ8UXokgREBFxGguA1hVVdUmBYwtTSaQbPMpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:19</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Up Side Down Tesla</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>135.291892573446</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK clone-ticker USDT; serial-deployer launches=38 &gt; 5</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>7vG48c29W1oAtAeUUpphLgQ2bDUWTiXokhrYF2zsX34p</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:40:41</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>niggi</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>niggi</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>135.291892573446</v>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=6 &gt; 5</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>3o1kTH57F6kuuhjcpMSuggQHRjxmThEri3iGnPXfpump</t>
+          <t>7WZMwGsTkRkGyHHcAyCA1bcS65eaAQrFMakUc1LVz6pE</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,12 +45,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="6">
@@ -67,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,14 +107,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -134,13 +134,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -619,7 +616,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +626,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +636,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -659,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +667,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +679,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+72.7%</t>
+          <t>+68.5%</t>
         </is>
       </c>
     </row>
@@ -694,7 +691,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +702,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +712,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2.202809591</v>
+        <v>1.025194494</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +722,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.2028095909999998</v>
+        <v>0.02519449399999996</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,63 +848,43 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Roadster Wif Wings</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>OKAY</t>
+          <t>RWW</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>-4.1%</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>+76.9%</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>-4.1%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr"/>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="12" t="n">
-        <v>0.958761799</v>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>-0.04123820099999997</v>
-      </c>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>trade-event breakeven -4.1%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>GHnGviuMzqMoBx8NuZNN3X5QDkYA7mZBu3xVGoPNmVzT</t>
+          <t>6oJLFN6wVz562HyB3LJHHxa2cG3fPr1DhBpD1gJ9pump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:24</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:50:25</t>
-        </is>
-      </c>
+          <t>2026-10-16 04:57:40</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -915,12 +892,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Flying Tesla Roadster 2.0</t>
+          <t>Crashed Tesla Roadster</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>FTR</t>
+          <t>CTR</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -930,7 +907,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>+24.4%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -947,166 +924,34 @@
         <v>1</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>1.244047792</v>
+        <v>1.025194494</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>0.2440477919999999</v>
+        <v>0.02519449399999996</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 24.4% (locked +25%, peak +68%)</t>
+          <t>trade-event ratchet-floor 2.5% (locked +25%, peak +69%)</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>J5s6eTHv3ZhzG5X4LrEwbr1LgRoj5tSmsZDrxntMpump</t>
+          <t>5VtDTJVXmbGZFuWtY8R1hmQ7nHpTLXuYDrqGzLXdbtf1</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:29</t>
+          <t>2026-10-16 04:57:54</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>numen.cash</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>NUMEN</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>GvEjB2Z24Hbq3Tf3F5e5vPgBpmV5p7YnL4SLDpoapump</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:50:31</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>p-null.si</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>p(null)</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>DuQU1Fi4KmT4cQgn1k1QYkqtYVEMRhEXbdijsipypump</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:50:37</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Cuck Coding</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Cuck</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>4RrzBXWpbXbSsTNHxDxEjffrSzuG4HPoSLwPr7yVpump</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:50:41</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:57:56</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1117,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1131,80 +976,116 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:50:34</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>Flying Tesla Roadster 2.0</t>
-        </is>
-      </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>FTR2,0</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>80.87747102079877</v>
-      </c>
-      <c r="E2" s="18" t="n">
-        <v>521.0370369380399</v>
-      </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 80.88% | 2- Total Locked Liquidity $521 | BLOCK insider-whale 151,660,777 tokens (&gt;= 100,000,000)</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="n">
-        <v>151660777.334045</v>
-      </c>
-      <c r="H2" s="16" t="inlineStr">
-        <is>
-          <t>7WZMwGsTkRkGyHHcAyCA1bcS65eaAQrFMakUc1LVz6pE</t>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:57:46</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Crashing Tesla Roadster</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=41 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>GNS1QtQ6Af34GXV7jpbaRw8qocRzQAqiVaDvTrdeGXsr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:57:48</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Tusla</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>TUSLA</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=10 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>GnHdHDdW6xaxRikhqUF6xPMfZAkwzABDHy1qcMdypump</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades.xlsx
+++ b/reports/pumpfun_trades.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +37,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -48,12 +48,8 @@
       <color rgb="001F4E79"/>
       <sz val="16"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,17 +63,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,8 +105,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -135,9 +126,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,7 +607,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -626,7 +617,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +627,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -656,7 +647,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +658,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -679,7 +670,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+68.5%</t>
+          <t>+4.1%</t>
         </is>
       </c>
     </row>
@@ -691,7 +682,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-1.9%</t>
         </is>
       </c>
     </row>
@@ -702,7 +693,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -712,7 +703,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1.025194494</v>
+        <v>5.70328915</v>
       </c>
     </row>
     <row r="21">
@@ -722,7 +713,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.02519449399999996</v>
+        <v>-0.2967108500000002</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -848,43 +839,63 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Roadster Wif Wings</t>
+          <t>Roadster League</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>RWW</t>
+          <t>RDSTR</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
+      <c r="I2" s="12" t="n">
+        <v>0.94128804</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>-0.05871196000000001</v>
+      </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog stop-loss -4.0%</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>6oJLFN6wVz562HyB3LJHHxa2cG3fPr1DhBpD1gJ9pump</t>
+          <t>9VEBn4L7TWDKh1hFpuQfTJZfr4bZpooGnDnXQP7Jpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:57:40</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr"/>
+          <t>2026-10-16 05:22:55</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:22:56</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -892,27 +903,27 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Crashed Tesla Roadster</t>
+          <t>ba-bump</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>+2.5%</t>
+          <t>BABUMP</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>+68.5%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -924,34 +935,290 @@
         <v>1</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>1.025194494</v>
+        <v>0.94128804</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>0.02519449399999996</v>
+        <v>-0.05871196000000001</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 2.5% (locked +25%, peak +69%)</t>
+          <t>watchdog stop-loss -4.0%</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>5VtDTJVXmbGZFuWtY8R1hmQ7nHpTLXuYDrqGzLXdbtf1</t>
+          <t>Fdxu4ssBWHeq6wjioCHKZSdZEiVh2pmLLBa9aEprpump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:57:54</t>
+          <t>2026-10-16 05:22:57</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:57:56</t>
+          <t>2026-10-16 05:22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Roadster League</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>+24.7%</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>1.071451193</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>0.07145119299999991</v>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 9.3% (-12.4% from peak, tol=10%)</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>DptdbbFwkLbKRCriN2sujYZkun7ZR7LfmSuocXgapump</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:22:58</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Roadster League</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>0.94128804</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>-0.05871196000000001</v>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -4.0%</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>6mtbYUmDMezp5KytZhZ6r25SQjckxupHkoWK7qnQpump</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:00</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Roadster League</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>0.94128804</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>-0.05871196000000001</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -4.0%</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>6zFh6gadfmR2iUhVGXZhJ3wgwEUanZ4i4VS9ZBFjpump</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:14</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Halo.fun</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>-13.3%</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>-11.6%</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>0.866685797</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>-0.133314203</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>watchdog stop-loss -11.6%</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>6vAYQrLWb4kKRGkDGEV6cVXWRvF273WA3XhXcv4Qpump</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:15</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -962,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1020,17 +1287,17 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>2026-10-16 04:57:46</t>
+          <t>2026-10-16 05:23:06</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Crashing Tesla Roadster</t>
+          <t>Roadster League</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>CTR</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
@@ -1041,7 +1308,7 @@
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=41 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=6 &gt; 5</t>
         </is>
       </c>
       <c r="G2" s="17" t="n">
@@ -1049,24 +1316,24 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>GNS1QtQ6Af34GXV7jpbaRw8qocRzQAqiVaDvTrdeGXsr</t>
+          <t>BmVRs1bTmsNQxCPY7ZafqGFsmsT1f8crJS2Xa2U3pump</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>2026-10-16 04:57:48</t>
+          <t>2026-10-16 05:23:12</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Tusla</t>
+          <t>Roadster League</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>TUSLA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D3" s="16" t="n">
@@ -1077,15 +1344,87 @@
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=10 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK insider-whale 153,285,714 tokens (&gt;= 100,000,000); sniper-bundle 10 wallets besides LP</t>
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0</v>
+        <v>153285714.285714</v>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>GnHdHDdW6xaxRikhqUF6xPMfZAkwzABDHy1qcMdypump</t>
+          <t>Dv8Z4Mnmq6wsPF3Y82MTDGSXMZVnQh9rL5rq9u2Dpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:17</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Roadster League</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>77.32066653540991</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>636.98458242588</v>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 77.32% | 2- Total Locked Liquidity $637 | BLOCK sniper-bundle 9 wallets besides LP</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>35804181.905251</v>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>arsE5wWTdHtFso8Pd5BM8wQ5xCmpKrA16Zm4YY2pump</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:23:19</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Roadster League</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>71.51749630032745</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>843.44000010543</v>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 71.52% | 2- Total Locked Liquidity $843 | BLOCK sniper-bundle 14 wallets besides LP</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>59172794.117647</v>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>HvcX5VL5SpWX6yQvJor65Jzf2xKcTgvr11Nq3HUNpump</t>
         </is>
       </c>
     </row>
